--- a/data/Matriz Pruebas Boton Pago.xlsx
+++ b/data/Matriz Pruebas Boton Pago.xlsx
@@ -2302,7 +2302,8 @@
       </c>
       <c r="M6" s="65" t="inlineStr">
         <is>
-          <t>Confirmado con desarrollo: al agotarse el token se genera uno nuevo y se reinicia el flujo, no se debe quedar en un error sin salida</t>
+          <t>Confirmado con desarrollo: al agotarse el token se genera uno nuevo y se reinicia el flujo, no se debe quedar en un error sin salida
+[Act. 29/09/2026] Automatizacion: se espera maximo 120 s; si el token no expira ni se reinicia el flujo en ese tiempo, se marca como 'Tiempo de espera excedido'</t>
         </is>
       </c>
     </row>
@@ -4750,7 +4751,8 @@
       </c>
       <c r="M45" s="60" t="inlineStr">
         <is>
-          <t>Mismo comportamiento esperado que al inicio del flujo (ver Modulo 1): token vencido = nuevo token automatico, nunca un error sin salida</t>
+          <t>Mismo comportamiento esperado que al inicio del flujo (ver Modulo 1): token vencido = nuevo token automatico, nunca un error sin salida
+[Act. 29/09/2026] Automatizacion: se espera maximo 120 s; si el token no expira ni se reinicia el flujo en ese tiempo, se marca como 'Tiempo de espera excedido'</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4814,11 @@
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M46" s="60" t="n"/>
+      <c r="M46" s="60" t="inlineStr">
+        <is>
+          <t>[Act. 29/09/2026] Automatizacion: requiere una tarjeta que deje el pago en proceso (3DS) para abrir el link en paralelo</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="75" customHeight="1" s="32">
       <c r="A47" s="60" t="inlineStr">
@@ -6009,7 +6015,7 @@
       </c>
       <c r="J65" s="65" t="inlineStr">
         <is>
-          <t>El resumen muestra nombre completo, correo, telefono, direccion, pais, estado, ciudad, codigo postal, la tarjeta enmascarada (solo ultimos 4) y el vencimiento, iguales a lo capturado</t>
+          <t>El resumen muestra nombre completo, correo, telefono, direccion, ciudad y codigo postal iguales a lo capturado; pais y estado con su nombre (Mexico, Puebla); la tarjeta enmascarada (solo ultimos 4) y el vencimiento en formato MM/AA</t>
         </is>
       </c>
       <c r="K65" s="65" t="n"/>
@@ -6020,7 +6026,8 @@
       </c>
       <c r="M65" s="65" t="inlineStr">
         <is>
-          <t>[Act. 29/09/2026] Caso nuevo</t>
+          <t>[Act. 29/09/2026] Caso nuevo
+[Act. 29/09/2026] Observado: Pais y Estado se muestran como codigo ('MEX', 'PUE') en lugar del nombre; el vencimiento se muestra '1226' sin diagonal (se capturo 12/26)</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6157,8 @@
       </c>
       <c r="M67" s="65" t="inlineStr">
         <is>
-          <t>[Act. 29/09/2026] Caso nuevo</t>
+          <t>[Act. 29/09/2026] Caso nuevo
+[Act. 29/09/2026] Observado: los numeros del indicador de pasos son solo informativos (no navegan aunque son botones). Confirmar con diseno si debe permitir navegar</t>
         </is>
       </c>
     </row>

--- a/data/Matriz Pruebas Boton Pago.xlsx
+++ b/data/Matriz Pruebas Boton Pago.xlsx
@@ -1527,7 +1527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:C38"/>
+  <dimension ref="B2:C39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -1599,7 +1599,7 @@
         </is>
       </c>
       <c r="C9" s="42" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
-          <t>2.0 - Revision 29/09/2026 (comentarios de revision incorporados)</t>
+          <t>2.1 - Revision 30/09/2026 (casos depurados; los IDs eliminados quedan vacios, sin renumerar)</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="C19" s="52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="32">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="C20" s="52" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="32">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="C21" s="52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="32">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="C23" s="52" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="32">
@@ -1743,7 +1743,7 @@
         </is>
       </c>
       <c r="C24" s="52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="32">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="C25" s="52" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="32">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="C28" s="52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="C29" s="52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="C30" s="52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="C31" s="52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="C32" s="52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C36" s="42" t="inlineStr">
         <is>
-          <t>Caso nuevo (no estaba en la version original de 49 casos). Total: 52</t>
+          <t>Caso nuevo (no estaba en la version original de 49 casos). Total: 28</t>
         </is>
       </c>
     </row>
@@ -1878,6 +1878,18 @@
       <c r="C38" s="42" t="inlineStr">
         <is>
           <t>Automatizada / Mixta (automatizada + Citeling manual) / Manual / Por automatizar</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>Fila vacia (solo ID)</t>
+        </is>
+      </c>
+      <c r="C39" s="42" t="inlineStr">
+        <is>
+          <t>Caso eliminado en la revision del 30/09/2026 (30 casos); el ID no se reutiliza</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1942,7 @@
         </is>
       </c>
       <c r="C6" s="46">
-        <f>COUNTA('Matriz de Pruebas'!A2:A500)</f>
+        <f>COUNTA('Matriz de Pruebas'!C2:C500)</f>
         <v/>
       </c>
     </row>
@@ -2634,75 +2646,25 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="75" customHeight="1" s="32">
-      <c r="A8" s="70" t="inlineStr">
+    <row r="8" ht="15" customHeight="1" s="32">
+      <c r="A8" s="73" t="inlineStr">
         <is>
           <t>TC-BP-051</t>
         </is>
       </c>
-      <c r="B8" s="70" t="inlineStr">
-        <is>
-          <t>01. Acceso con Referencia / Linea de Captura (inicio del alcance QA)</t>
-        </is>
-      </c>
-      <c r="C8" s="70" t="inlineStr">
-        <is>
-          <t>Verificar la informacion del encabezado del pago</t>
-        </is>
-      </c>
-      <c r="D8" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E8" s="72" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F8" s="70" t="inlineStr">
-        <is>
-          <t>Se ingreso con una referencia o linea de captura vigente y se muestra el Paso 1 - Contacto</t>
-        </is>
-      </c>
-      <c r="G8" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H8" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Revisar importe, concepto, fecha, solicitante, descripcion y referencia del encabezado</t>
-        </is>
-      </c>
-      <c r="I8" s="70" t="inlineStr">
-        <is>
-          <t>Referencia o linea de captura vigente</t>
-        </is>
-      </c>
-      <c r="J8" s="70" t="inlineStr">
-        <is>
-          <t>El encabezado muestra importe, concepto, fecha, solicitante, descripcion y referencia correctos y sin campos vacios</t>
-        </is>
-      </c>
-      <c r="K8" s="70" t="n"/>
-      <c r="L8" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M8" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Observado: 'Solicitante' aparece vacio y el concepto dice 'Pago en Linea' aunque la descripcion es PREDIAL
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N8" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="B8" s="73" t="n"/>
+      <c r="C8" s="73" t="n"/>
+      <c r="D8" s="74" t="n"/>
+      <c r="E8" s="75" t="n"/>
+      <c r="F8" s="73" t="n"/>
+      <c r="G8" s="73" t="n"/>
+      <c r="H8" s="73" t="n"/>
+      <c r="I8" s="73" t="n"/>
+      <c r="J8" s="73" t="n"/>
+      <c r="K8" s="73" t="n"/>
+      <c r="L8" s="73" t="n"/>
+      <c r="M8" s="73" t="n"/>
+      <c r="N8" s="73" t="n"/>
     </row>
     <row r="9" ht="75" customHeight="1" s="32">
       <c r="A9" s="73" t="inlineStr">
@@ -3349,77 +3311,25 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="75" customHeight="1" s="32">
-      <c r="A18" s="70" t="inlineStr">
+    <row r="18" ht="15" customHeight="1" s="32">
+      <c r="A18" s="73" t="inlineStr">
         <is>
           <t>TC-BP-055</t>
         </is>
       </c>
-      <c r="B18" s="70" t="inlineStr">
-        <is>
-          <t>02. Paso 1 - Datos de Contacto</t>
-        </is>
-      </c>
-      <c r="C18" s="70" t="inlineStr">
-        <is>
-          <t>Capturar un telefono solo con letras</t>
-        </is>
-      </c>
-      <c r="D18" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E18" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F18" s="70" t="inlineStr">
-        <is>
-          <t>Se ingreso con una referencia o linea de captura vigente y se muestra el Paso 1 - Contacto</t>
-        </is>
-      </c>
-      <c r="G18" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H18" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Escribir 'abcdefghij' en el telefono
-3. Capturar un correo valido
-4. Dar clic en 'Continuar'</t>
-        </is>
-      </c>
-      <c r="I18" s="70" t="inlineStr">
-        <is>
-          <t>Telefono: abcdefghij</t>
-        </is>
-      </c>
-      <c r="J18" s="70" t="inlineStr">
-        <is>
-          <t>El campo rechaza las letras o muestra un mensaje de telefono invalido</t>
-        </is>
-      </c>
-      <c r="K18" s="70" t="n"/>
-      <c r="L18" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M18" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Riesgo: al quitar las letras el campo queda vacio y la validacion lo toma como 'sin telefono'
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N18" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="B18" s="73" t="n"/>
+      <c r="C18" s="73" t="n"/>
+      <c r="D18" s="74" t="n"/>
+      <c r="E18" s="75" t="n"/>
+      <c r="F18" s="73" t="n"/>
+      <c r="G18" s="73" t="n"/>
+      <c r="H18" s="73" t="n"/>
+      <c r="I18" s="73" t="n"/>
+      <c r="J18" s="73" t="n"/>
+      <c r="K18" s="73" t="n"/>
+      <c r="L18" s="73" t="n"/>
+      <c r="M18" s="73" t="n"/>
+      <c r="N18" s="73" t="n"/>
     </row>
     <row r="19" ht="75" customHeight="1" s="32">
       <c r="A19" s="73" t="inlineStr">
@@ -3545,7 +3455,7 @@
       </c>
       <c r="J20" s="73" t="inlineStr">
         <is>
-          <t>El sistema no avanza; muestra 'Este campo es requerido' en calle, codigo postal, ciudad y estado</t>
+          <t>El sistema no avanza y el navegador muestra el aviso 'Please select an item in the list.' en el campo Estado</t>
         </is>
       </c>
       <c r="K20" s="73" t="n"/>
@@ -3558,7 +3468,8 @@
         <is>
           <t>[Act. 29/09/2026] Actualizado con las pantallas reales
 [Act. 29/09/2026] Observado: el Estado usa la validacion nativa del navegador ('Please select an item in the list.', en ingles) y bloquea los mensajes de la pagina
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
+[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)
+[Revision 30/09/2026] Resultado esperado ajustado: el aviso 'Please select an item in the list.' es el comportamiento correcto</t>
         </is>
       </c>
       <c r="N20" s="73" t="inlineStr">
@@ -3652,7 +3563,7 @@
       </c>
       <c r="C22" s="73" t="inlineStr">
         <is>
-          <t>Ingresar un codigo postal que no existe en el catalogo</t>
+          <t>Ingresar un codigo postal con menos digitos (123)</t>
         </is>
       </c>
       <c r="D22" s="74" t="inlineStr">
@@ -3679,18 +3590,18 @@
         <is>
           <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
 2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2: escribir '00000' en Codigo Postal y llenar el resto con datos validos
+3. Paso 2: escribir '123' en Codigo Postal y llenar el resto con datos validos
 4. Dar clic en 'Continuar'</t>
         </is>
       </c>
       <c r="I22" s="73" t="inlineStr">
         <is>
-          <t>CP: 00000</t>
+          <t>CP: 123</t>
         </is>
       </c>
       <c r="J22" s="73" t="inlineStr">
         <is>
-          <t>El sistema avisa que no encontro colonias para ese codigo postal y permite corregirlo</t>
+          <t>El sistema muestra 'Debe ser un codigo postal valido.' y no permite avanzar</t>
         </is>
       </c>
       <c r="K22" s="73" t="n"/>
@@ -3702,7 +3613,8 @@
       <c r="M22" s="73" t="inlineStr">
         <is>
           <t>[Act. 29/09/2026] El validador actual solo revisa el formato (5 digitos); no consulta un catalogo de codigos postales
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
+[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)
+[Revision 30/09/2026] Caso ajustado: antes validaba el CP 00000 (catalogo); ahora valida un CP con menos digitos</t>
         </is>
       </c>
       <c r="N22" s="73" t="inlineStr">
@@ -3835,7 +3747,7 @@
       </c>
       <c r="J24" s="70" t="inlineStr">
         <is>
-          <t>El sistema no avanza y muestra 'Este campo es requerido' en Estado</t>
+          <t>El sistema no avanza y el navegador muestra el aviso 'Please select an item in the list.' en el campo Estado</t>
         </is>
       </c>
       <c r="K24" s="70" t="n"/>
@@ -3847,7 +3759,8 @@
       <c r="M24" s="70" t="inlineStr">
         <is>
           <t>[CASO NUEVO] [Act. 29/09/2026] Observado: el Estado usa la validacion nativa del navegador ('Please select an item in the list.', en ingles) y bloquea los mensajes de la pagina
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
+[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)
+[Revision 30/09/2026] Resultado esperado ajustado: el aviso 'Please select an item in the list.' es el comportamiento correcto</t>
         </is>
       </c>
       <c r="N24" s="70" t="inlineStr">
@@ -3856,78 +3769,25 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="75" customHeight="1" s="32">
-      <c r="A25" s="70" t="inlineStr">
+    <row r="25" ht="15" customHeight="1" s="32">
+      <c r="A25" s="73" t="inlineStr">
         <is>
           <t>TC-BP-057</t>
         </is>
       </c>
-      <c r="B25" s="70" t="inlineStr">
-        <is>
-          <t>03. Paso 2 - Direccion</t>
-        </is>
-      </c>
-      <c r="C25" s="70" t="inlineStr">
-        <is>
-          <t>Capturar calle y ciudad con acentos y simbolos comunes</t>
-        </is>
-      </c>
-      <c r="D25" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E25" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F25" s="70" t="inlineStr">
-        <is>
-          <t>El Paso 1 - Contacto fue completado y confirmado correctamente</t>
-        </is>
-      </c>
-      <c r="G25" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H25" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2: escribir 'Av. Juárez #12' en Calle y 'Tehuacán' en Ciudad
-4. Revisar lo que quedo escrito
-5. Continuar hasta el Paso 4 y revisar el resumen</t>
-        </is>
-      </c>
-      <c r="I25" s="70" t="inlineStr">
-        <is>
-          <t>Calle: Av. Juárez #12 / Ciudad: Tehuacán</t>
-        </is>
-      </c>
-      <c r="J25" s="70" t="inlineStr">
-        <is>
-          <t>El sistema acepta el dato o avisa claramente; nunca modifica en silencio lo que escribio el usuario</t>
-        </is>
-      </c>
-      <c r="K25" s="70" t="n"/>
-      <c r="L25" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M25" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Los campos solo permiten letras sin acento, numeros y espacios: se borran acentos, '#', '.' y ','
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N25" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="B25" s="73" t="n"/>
+      <c r="C25" s="73" t="n"/>
+      <c r="D25" s="74" t="n"/>
+      <c r="E25" s="75" t="n"/>
+      <c r="F25" s="73" t="n"/>
+      <c r="G25" s="73" t="n"/>
+      <c r="H25" s="73" t="n"/>
+      <c r="I25" s="73" t="n"/>
+      <c r="J25" s="73" t="n"/>
+      <c r="K25" s="73" t="n"/>
+      <c r="L25" s="73" t="n"/>
+      <c r="M25" s="73" t="n"/>
+      <c r="N25" s="73" t="n"/>
     </row>
     <row r="26" ht="75" customHeight="1" s="32">
       <c r="A26" s="70" t="inlineStr">
@@ -4603,7 +4463,7 @@
       </c>
       <c r="C35" s="70" t="inlineStr">
         <is>
-          <t>Capturar nombre y apellido compuestos (con espacio)</t>
+          <t>Capturar un apellido compuesto (con espacio): solo se permite un apellido</t>
         </is>
       </c>
       <c r="D35" s="71" t="inlineStr">
@@ -4631,18 +4491,18 @@
           <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
 2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
 3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3: escribir 'Juan Carlos' en Nombre y 'Pérez López' en Apellido
+4. Paso 3: escribir 'Juan' en Nombre y 'Pérez López' en Apellido
 5. Llenar el resto con datos validos y dar clic en 'Continuar'</t>
         </is>
       </c>
       <c r="I35" s="70" t="inlineStr">
         <is>
-          <t>Nombre: Juan Carlos / Apellido: Pérez López / VISA 4111 1111 1111 1111</t>
+          <t>Nombre: Juan / Apellido: Pérez López</t>
         </is>
       </c>
       <c r="J35" s="70" t="inlineStr">
         <is>
-          <t>El sistema acepta nombres y apellidos compuestos, como el ejemplo que muestra el propio campo</t>
+          <t>El sistema no avanza y muestra 'Solo se permiten letras con acentos' en Apellido: solo se permite un apellido</t>
         </is>
       </c>
       <c r="K35" s="70" t="n"/>
@@ -4654,7 +4514,8 @@
       <c r="M35" s="70" t="inlineStr">
         <is>
           <t>[CASO NUEVO] La validacion actual no permite espacios: el propio ejemplo 'Perez Lopez' marca error
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
+[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)
+[Revision 30/09/2026] Resultado esperado ajustado: el mensaje 'Solo se permiten letras con acentos' indica que la prueba es exitosa (un solo apellido)</t>
         </is>
       </c>
       <c r="N35" s="70" t="inlineStr">
@@ -5178,117 +5039,157 @@
         </is>
       </c>
     </row>
-    <row r="43" ht="105" customHeight="1" s="32">
+    <row r="43" ht="15" customHeight="1" s="32">
       <c r="A43" s="73" t="inlineStr">
         <is>
           <t>TC-BP-028</t>
         </is>
       </c>
-      <c r="B43" s="73" t="inlineStr">
+      <c r="B43" s="73" t="n"/>
+      <c r="C43" s="73" t="n"/>
+      <c r="D43" s="74" t="n"/>
+      <c r="E43" s="75" t="n"/>
+      <c r="F43" s="73" t="n"/>
+      <c r="G43" s="73" t="n"/>
+      <c r="H43" s="73" t="n"/>
+      <c r="I43" s="73" t="n"/>
+      <c r="J43" s="73" t="n"/>
+      <c r="K43" s="73" t="n"/>
+      <c r="L43" s="73" t="n"/>
+      <c r="M43" s="73" t="n"/>
+      <c r="N43" s="73" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="32">
+      <c r="A44" s="73" t="inlineStr">
+        <is>
+          <t>TC-BP-095</t>
+        </is>
+      </c>
+      <c r="B44" s="73" t="n"/>
+      <c r="C44" s="73" t="n"/>
+      <c r="D44" s="74" t="n"/>
+      <c r="E44" s="75" t="n"/>
+      <c r="F44" s="73" t="n"/>
+      <c r="G44" s="73" t="n"/>
+      <c r="H44" s="73" t="n"/>
+      <c r="I44" s="73" t="n"/>
+      <c r="J44" s="73" t="n"/>
+      <c r="K44" s="73" t="n"/>
+      <c r="L44" s="73" t="n"/>
+      <c r="M44" s="73" t="n"/>
+      <c r="N44" s="73" t="n"/>
+    </row>
+    <row r="45" ht="120" customHeight="1" s="32">
+      <c r="A45" s="70" t="inlineStr">
+        <is>
+          <t>TC-BP-096</t>
+        </is>
+      </c>
+      <c r="B45" s="70" t="inlineStr">
         <is>
           <t>05. Procesamiento del Pago y Autenticacion del Banco (3D Secure)</t>
         </is>
       </c>
-      <c r="C43" s="73" t="inlineStr">
-        <is>
-          <t>El usuario tarda demasiado en responder en la pantalla del banco</t>
-        </is>
-      </c>
-      <c r="D43" s="74" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E43" s="75" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F43" s="73" t="inlineStr">
-        <is>
-          <t>Pago enviado a procesar; el banco esta solicitando 3D Secure</t>
-        </is>
-      </c>
-      <c r="G43" s="73" t="inlineStr">
-        <is>
-          <t>Si - tarjeta 'Challenge' (el banco pide un codigo)</t>
-        </is>
-      </c>
-      <c r="H43" s="73" t="inlineStr">
+      <c r="C45" s="70" t="inlineStr">
+        <is>
+          <t>Pago con tarjeta 'Not authenticated' (autenticacion fallida)</t>
+        </is>
+      </c>
+      <c r="D45" s="71" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="E45" s="72" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="F45" s="70" t="inlineStr">
+        <is>
+          <t>Se cuenta con una referencia o linea de captura vigente y sin pagar del Gobierno de Puebla</t>
+        </is>
+      </c>
+      <c r="G45" s="70" t="inlineStr">
+        <is>
+          <t>Si - tarjeta 'Not authenticated' (el banco rechaza la autenticacion)</t>
+        </is>
+      </c>
+      <c r="H45" s="70" t="inlineStr">
         <is>
           <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
 2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
 3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
+4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, la tarjeta de prueba indicada, vencimiento y CVV y dar clic en 'Continuar'
 5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. En la pagina del banco (3D Secure) no hacer nada durante varios minutos
-7. Revisar el resultado</t>
-        </is>
-      </c>
-      <c r="I43" s="73" t="inlineStr">
-        <is>
-          <t>VISA 4110 7600 0000 0008 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J43" s="73" t="inlineStr">
-        <is>
-          <t>El sistema muestra un mensaje de tiempo agotado y permite reintentar el pago sin cobrar dos veces</t>
-        </is>
-      </c>
-      <c r="K43" s="73" t="n"/>
-      <c r="L43" s="73" t="inlineStr">
+6. Verificar que el banco no pida codigo
+7. Revisar 'Transaccion rechazada', el aviso emergente y el boton 'Reintentar'</t>
+        </is>
+      </c>
+      <c r="I45" s="70" t="inlineStr">
+        <is>
+          <t>VISA 4110 7600 0000 0065 / vencimiento futuro (ej. 12/30) / CVV 123 (alterna: MasterCard 5180 3000 0000 0039)</t>
+        </is>
+      </c>
+      <c r="J45" s="70" t="inlineStr">
+        <is>
+          <t>Se muestra 'Transaccion rechazada' ('Rechazada por 3DS'), el aviso de error y el boton 'Reintentar'; no se registra cobro</t>
+        </is>
+      </c>
+      <c r="K45" s="70" t="n"/>
+      <c r="L45" s="70" t="inlineStr">
         <is>
           <t>Pendiente</t>
         </is>
       </c>
-      <c r="M43" s="76" t="inlineStr">
-        <is>
-          <t>[Revision 29/09/2026] Por validar si aplica: confirmar si el banco maneja tiempo limite en el 3D Secure y como regresa al Boton de Pago</t>
-        </is>
-      </c>
-      <c r="N43" s="73" t="inlineStr">
+      <c r="M45" s="70" t="inlineStr">
+        <is>
+          <t>[CASO NUEVO] Tarjeta de prueba 3DS (ver hoja 'Tarjetas 3DS')</t>
+        </is>
+      </c>
+      <c r="N45" s="70" t="inlineStr">
         <is>
           <t>Automatizada</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="120" customHeight="1" s="32">
-      <c r="A44" s="70" t="inlineStr">
-        <is>
-          <t>TC-BP-095</t>
-        </is>
-      </c>
-      <c r="B44" s="70" t="inlineStr">
+    <row r="46" ht="120" customHeight="1" s="32">
+      <c r="A46" s="70" t="inlineStr">
+        <is>
+          <t>TC-BP-097</t>
+        </is>
+      </c>
+      <c r="B46" s="70" t="inlineStr">
         <is>
           <t>05. Procesamiento del Pago y Autenticacion del Banco (3D Secure)</t>
         </is>
       </c>
-      <c r="C44" s="70" t="inlineStr">
-        <is>
-          <t>Pago con tarjeta 'Attempt' (autenticacion intentada)</t>
-        </is>
-      </c>
-      <c r="D44" s="71" t="inlineStr">
+      <c r="C46" s="70" t="inlineStr">
+        <is>
+          <t>Pago sin reto con MasterCard (tarjeta 'Not challenge')</t>
+        </is>
+      </c>
+      <c r="D46" s="71" t="inlineStr">
         <is>
           <t>EXITO</t>
         </is>
       </c>
-      <c r="E44" s="72" t="inlineStr">
+      <c r="E46" s="72" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="F44" s="70" t="inlineStr">
+      <c r="F46" s="70" t="inlineStr">
         <is>
           <t>Se cuenta con una referencia o linea de captura vigente y sin pagar del Gobierno de Puebla</t>
         </is>
       </c>
-      <c r="G44" s="70" t="inlineStr">
-        <is>
-          <t>Si - tarjeta 'Attempt' (autenticacion intentada, sin reto)</t>
-        </is>
-      </c>
-      <c r="H44" s="70" t="inlineStr">
+      <c r="G46" s="70" t="inlineStr">
+        <is>
+          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
+        </is>
+      </c>
+      <c r="H46" s="70" t="inlineStr">
         <is>
           <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
 2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
@@ -5300,155 +5201,6 @@
 8. (Manual) Ingresar a Citeling y verificar que el pago aparezca con la referencia, importe, autorizacion, fecha y tipo de pago</t>
         </is>
       </c>
-      <c r="I44" s="70" t="inlineStr">
-        <is>
-          <t>VISA 4110 7600 0000 0040 / vencimiento futuro (ej. 12/30) / CVV 123 (alterna: MasterCard 5180 3000 0000 0054)</t>
-        </is>
-      </c>
-      <c r="J44" s="70" t="inlineStr">
-        <is>
-          <t>El pago se aprueba sin pedir codigo al usuario y se muestra 'Transaccion aprobada'</t>
-        </is>
-      </c>
-      <c r="K44" s="70" t="n"/>
-      <c r="L44" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M44" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Tarjeta de prueba 3DS (ver hoja 'Tarjetas 3DS')</t>
-        </is>
-      </c>
-      <c r="N44" s="70" t="inlineStr">
-        <is>
-          <t>Mixta (automatizada + Citeling manual)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="120" customHeight="1" s="32">
-      <c r="A45" s="70" t="inlineStr">
-        <is>
-          <t>TC-BP-096</t>
-        </is>
-      </c>
-      <c r="B45" s="70" t="inlineStr">
-        <is>
-          <t>05. Procesamiento del Pago y Autenticacion del Banco (3D Secure)</t>
-        </is>
-      </c>
-      <c r="C45" s="70" t="inlineStr">
-        <is>
-          <t>Pago con tarjeta 'Not authenticated' (autenticacion fallida)</t>
-        </is>
-      </c>
-      <c r="D45" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E45" s="72" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F45" s="70" t="inlineStr">
-        <is>
-          <t>Se cuenta con una referencia o linea de captura vigente y sin pagar del Gobierno de Puebla</t>
-        </is>
-      </c>
-      <c r="G45" s="70" t="inlineStr">
-        <is>
-          <t>Si - tarjeta 'Not authenticated' (el banco rechaza la autenticacion)</t>
-        </is>
-      </c>
-      <c r="H45" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, la tarjeta de prueba indicada, vencimiento y CVV y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Verificar que el banco no pida codigo
-7. Revisar 'Transaccion rechazada', el aviso emergente y el boton 'Reintentar'</t>
-        </is>
-      </c>
-      <c r="I45" s="70" t="inlineStr">
-        <is>
-          <t>VISA 4110 7600 0000 0065 / vencimiento futuro (ej. 12/30) / CVV 123 (alterna: MasterCard 5180 3000 0000 0039)</t>
-        </is>
-      </c>
-      <c r="J45" s="70" t="inlineStr">
-        <is>
-          <t>Se muestra 'Transaccion rechazada' ('Rechazada por 3DS'), el aviso de error y el boton 'Reintentar'; no se registra cobro</t>
-        </is>
-      </c>
-      <c r="K45" s="70" t="n"/>
-      <c r="L45" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M45" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Tarjeta de prueba 3DS (ver hoja 'Tarjetas 3DS')</t>
-        </is>
-      </c>
-      <c r="N45" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="120" customHeight="1" s="32">
-      <c r="A46" s="70" t="inlineStr">
-        <is>
-          <t>TC-BP-097</t>
-        </is>
-      </c>
-      <c r="B46" s="70" t="inlineStr">
-        <is>
-          <t>05. Procesamiento del Pago y Autenticacion del Banco (3D Secure)</t>
-        </is>
-      </c>
-      <c r="C46" s="70" t="inlineStr">
-        <is>
-          <t>Pago sin reto con MasterCard (tarjeta 'Not challenge')</t>
-        </is>
-      </c>
-      <c r="D46" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E46" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F46" s="70" t="inlineStr">
-        <is>
-          <t>Se cuenta con una referencia o linea de captura vigente y sin pagar del Gobierno de Puebla</t>
-        </is>
-      </c>
-      <c r="G46" s="70" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H46" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, la tarjeta de prueba indicada, vencimiento y CVV y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Verificar que el banco no pida codigo (si redirige, regresa solo)
-7. Revisar el resultado
-8. (Manual) Ingresar a Citeling y verificar que el pago aparezca con la referencia, importe, autorizacion, fecha y tipo de pago</t>
-        </is>
-      </c>
       <c r="I46" s="70" t="inlineStr">
         <is>
           <t>MasterCard 5180 3000 0000 0005 / vencimiento futuro (ej. 12/30) / CVV 123</t>
@@ -5551,236 +5303,65 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="90" customHeight="1" s="32">
+    <row r="48" ht="15" customHeight="1" s="32">
       <c r="A48" s="73" t="inlineStr">
         <is>
           <t>TC-BP-029</t>
         </is>
       </c>
-      <c r="B48" s="73" t="inlineStr">
-        <is>
-          <t>06. Resultado Exitoso (fin del alcance QA - redireccion al Gobierno)</t>
-        </is>
-      </c>
-      <c r="C48" s="73" t="inlineStr">
-        <is>
-          <t>Verificar la pantalla de 'Transaccion aprobada'</t>
-        </is>
-      </c>
-      <c r="D48" s="74" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E48" s="75" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F48" s="73" t="inlineStr">
-        <is>
-          <t>El pago fue enviado al banco y aprobado (con o sin 3D Secure, segun la tarjeta de prueba usada)</t>
-        </is>
-      </c>
-      <c r="G48" s="73" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H48" s="73" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Si el banco lo solicita, completar la autenticacion 3D Secure en la pagina del banco
-7. Revisar 'Transaccion aprobada': Estado, Codigo de respuesta, Referencia, Autorizacion e Identificador
-8. (Manual) Ingresar a Citeling y verificar que el pago aparezca con la referencia, importe, autorizacion, fecha y tipo de pago</t>
-        </is>
-      </c>
-      <c r="I48" s="73" t="inlineStr">
-        <is>
-          <t>VISA 4111 1111 1111 1111 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J48" s="73" t="inlineStr">
-        <is>
-          <t>Se muestra 'Transaccion aprobada' con Estado, Codigo de respuesta, Referencia, Autorizacion e Identificador, y el pago se refleja en Citeling con los mismos datos</t>
-        </is>
-      </c>
+      <c r="B48" s="73" t="n"/>
+      <c r="C48" s="73" t="n"/>
+      <c r="D48" s="74" t="n"/>
+      <c r="E48" s="75" t="n"/>
+      <c r="F48" s="73" t="n"/>
+      <c r="G48" s="73" t="n"/>
+      <c r="H48" s="73" t="n"/>
+      <c r="I48" s="73" t="n"/>
+      <c r="J48" s="73" t="n"/>
       <c r="K48" s="73" t="n"/>
-      <c r="L48" s="73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M48" s="73" t="inlineStr">
-        <is>
-          <t>[Act. 29/09/2026] Actualizado con las pantallas reales
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N48" s="73" t="inlineStr">
-        <is>
-          <t>Mixta (automatizada + Citeling manual)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="105" customHeight="1" s="32">
+      <c r="L48" s="73" t="n"/>
+      <c r="M48" s="73" t="n"/>
+      <c r="N48" s="73" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="32">
       <c r="A49" s="73" t="inlineStr">
         <is>
           <t>TC-BP-030</t>
         </is>
       </c>
-      <c r="B49" s="73" t="inlineStr">
-        <is>
-          <t>06. Resultado Exitoso (fin del alcance QA - redireccion al Gobierno)</t>
-        </is>
-      </c>
-      <c r="C49" s="73" t="inlineStr">
-        <is>
-          <t>Esperar a que el contador regresivo llegue a cero y se redirija al Gobierno de Puebla</t>
-        </is>
-      </c>
-      <c r="D49" s="74" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E49" s="75" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F49" s="73" t="inlineStr">
-        <is>
-          <t>El pago fue enviado al banco y aprobado (con o sin 3D Secure, segun la tarjeta de prueba usada)</t>
-        </is>
-      </c>
-      <c r="G49" s="73" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H49" s="73" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Si el banco lo solicita, completar la autenticacion 3D Secure en la pagina del banco
-7. En 'Transaccion aprobada' no hacer nada y dejar correr el contador de 10 segundos
-8. Verificar la redireccion al sitio del Gobierno de Puebla</t>
-        </is>
-      </c>
-      <c r="I49" s="73" t="inlineStr">
-        <is>
-          <t>VISA 4111 1111 1111 1111 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J49" s="73" t="inlineStr">
-        <is>
-          <t>Se muestra '¡No cierres esta ventana!' con un contador de 10 segundos; al llegar a cero se redirige al 'COMPROBANTE DE PAGO' del portal del Gobierno de Puebla</t>
-        </is>
-      </c>
+      <c r="B49" s="73" t="n"/>
+      <c r="C49" s="73" t="n"/>
+      <c r="D49" s="74" t="n"/>
+      <c r="E49" s="75" t="n"/>
+      <c r="F49" s="73" t="n"/>
+      <c r="G49" s="73" t="n"/>
+      <c r="H49" s="73" t="n"/>
+      <c r="I49" s="73" t="n"/>
+      <c r="J49" s="73" t="n"/>
       <c r="K49" s="73" t="n"/>
-      <c r="L49" s="73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M49" s="73" t="inlineStr">
-        <is>
-          <t>Fin del alcance de QA de Memphis: solo se valida que la redireccion ocurra correctamente; el contenido de la pagina destino del Gobierno de Puebla NO forma parte de esta matriz
-[Act. 29/09/2026] Actualizado con las pantallas reales
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)
-[Revision 29/09/2026] La redireccion termina en el 'COMPROBANTE DE PAGO' del Gobierno (ver TC-BP-099 a 101)</t>
-        </is>
-      </c>
-      <c r="N49" s="73" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="165" customHeight="1" s="32">
+      <c r="L49" s="73" t="n"/>
+      <c r="M49" s="73" t="n"/>
+      <c r="N49" s="73" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="32">
       <c r="A50" s="73" t="inlineStr">
         <is>
           <t>TC-BP-031</t>
         </is>
       </c>
-      <c r="B50" s="73" t="inlineStr">
-        <is>
-          <t>06. Resultado Exitoso (fin del alcance QA - redireccion al Gobierno)</t>
-        </is>
-      </c>
-      <c r="C50" s="73" t="inlineStr">
-        <is>
-          <t>Dar clic en 'Continuar' antes de que termine el contador</t>
-        </is>
-      </c>
-      <c r="D50" s="74" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E50" s="75" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F50" s="73" t="inlineStr">
-        <is>
-          <t>El pago fue enviado al banco y aprobado (con o sin 3D Secure, segun la tarjeta de prueba usada)</t>
-        </is>
-      </c>
-      <c r="G50" s="73" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H50" s="73" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Si el banco lo solicita, completar la autenticacion 3D Secure en la pagina del banco
-7. En 'Transaccion aprobada' dar clic en 'Continuar en N s.' antes de que termine el contador
-8. Verificar la redireccion inmediata al sitio del Gobierno</t>
-        </is>
-      </c>
-      <c r="I50" s="73" t="inlineStr">
-        <is>
-          <t>VISA 4111 1111 1111 1111 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J50" s="73" t="inlineStr">
-        <is>
-          <t>El sistema redirige de inmediato al 'COMPROBANTE DE PAGO' del portal del Gobierno, sin esperar a que termine el conteo</t>
-        </is>
-      </c>
+      <c r="B50" s="73" t="n"/>
+      <c r="C50" s="73" t="n"/>
+      <c r="D50" s="74" t="n"/>
+      <c r="E50" s="75" t="n"/>
+      <c r="F50" s="73" t="n"/>
+      <c r="G50" s="73" t="n"/>
+      <c r="H50" s="73" t="n"/>
+      <c r="I50" s="73" t="n"/>
+      <c r="J50" s="73" t="n"/>
       <c r="K50" s="73" t="n"/>
-      <c r="L50" s="73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M50" s="73" t="inlineStr">
-        <is>
-          <t>[Act. 29/09/2026] Actualizado con las pantallas reales
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)
-[Revision 29/09/2026] La redireccion termina en el 'COMPROBANTE DE PAGO' del Gobierno (ver TC-BP-099 a 101)</t>
-        </is>
-      </c>
-      <c r="N50" s="73" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="L50" s="73" t="n"/>
+      <c r="M50" s="73" t="n"/>
+      <c r="N50" s="73" t="n"/>
     </row>
     <row r="51" ht="90" customHeight="1" s="32">
       <c r="A51" s="70" t="inlineStr">
@@ -5926,226 +5507,65 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="120" customHeight="1" s="32">
-      <c r="A53" s="70" t="inlineStr">
+    <row r="53" ht="15" customHeight="1" s="32">
+      <c r="A53" s="73" t="inlineStr">
         <is>
           <t>TC-BP-100</t>
         </is>
       </c>
-      <c r="B53" s="70" t="inlineStr">
-        <is>
-          <t>06. Resultado Exitoso (fin del alcance QA - redireccion al Gobierno)</t>
-        </is>
-      </c>
-      <c r="C53" s="70" t="inlineStr">
-        <is>
-          <t>Descargar el PDF del Comprobante de Pago</t>
-        </is>
-      </c>
-      <c r="D53" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E53" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F53" s="70" t="inlineStr">
-        <is>
-          <t>Se cuenta con una referencia o linea de captura vigente y sin pagar del Gobierno de Puebla</t>
-        </is>
-      </c>
-      <c r="G53" s="70" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H53" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Completar los Pasos 1, 2 y 3 con datos validos (tarjeta 'Not challenge') hasta el Paso 4 - Pago
-3. Paso 4 - Pago: dar clic en 'Continuar' para pagar
-4. En 'Transaccion aprobada' anotar la Autorizacion y esperar el contador (o dar 'Continuar en N s.')
-5. Verificar que se muestre el 'COMPROBANTE DE PAGO' del Gobierno
-6. Dar clic en el boton 'Comprobante de Pago'
-7. (Manual) Revisar el contenido del PDF</t>
-        </is>
-      </c>
-      <c r="I53" s="70" t="inlineStr">
-        <is>
-          <t>VISA 4111 1111 1111 1111 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J53" s="70" t="inlineStr">
-        <is>
-          <t>Se abre o descarga el PDF del comprobante con referencia, importe, autorizacion y fecha correctos</t>
-        </is>
-      </c>
-      <c r="K53" s="70" t="n"/>
-      <c r="L53" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M53" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N53" s="70" t="inlineStr">
-        <is>
-          <t>Mixta (automatizada + revision manual del PDF)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="105" customHeight="1" s="32">
-      <c r="A54" s="70" t="inlineStr">
+      <c r="B53" s="73" t="n"/>
+      <c r="C53" s="73" t="n"/>
+      <c r="D53" s="74" t="n"/>
+      <c r="E53" s="75" t="n"/>
+      <c r="F53" s="73" t="n"/>
+      <c r="G53" s="73" t="n"/>
+      <c r="H53" s="73" t="n"/>
+      <c r="I53" s="73" t="n"/>
+      <c r="J53" s="73" t="n"/>
+      <c r="K53" s="73" t="n"/>
+      <c r="L53" s="73" t="n"/>
+      <c r="M53" s="73" t="n"/>
+      <c r="N53" s="73" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="32">
+      <c r="A54" s="73" t="inlineStr">
         <is>
           <t>TC-BP-101</t>
         </is>
       </c>
-      <c r="B54" s="70" t="inlineStr">
-        <is>
-          <t>06. Resultado Exitoso (fin del alcance QA - redireccion al Gobierno)</t>
-        </is>
-      </c>
-      <c r="C54" s="70" t="inlineStr">
-        <is>
-          <t>Regresar al inicio del portal desde el Comprobante de Pago</t>
-        </is>
-      </c>
-      <c r="D54" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E54" s="72" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F54" s="70" t="inlineStr">
-        <is>
-          <t>Se cuenta con una referencia o linea de captura vigente y sin pagar del Gobierno de Puebla</t>
-        </is>
-      </c>
-      <c r="G54" s="70" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H54" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Completar los Pasos 1, 2 y 3 con datos validos (tarjeta 'Not challenge') hasta el Paso 4 - Pago
-3. Paso 4 - Pago: dar clic en 'Continuar' para pagar
-4. En 'Transaccion aprobada' anotar la Autorizacion y esperar el contador (o dar 'Continuar en N s.')
-5. Verificar que se muestre el 'COMPROBANTE DE PAGO' del Gobierno
-6. Dar clic en el boton 'Inicio'</t>
-        </is>
-      </c>
-      <c r="I54" s="70" t="inlineStr">
-        <is>
-          <t>VISA 4111 1111 1111 1111 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J54" s="70" t="inlineStr">
-        <is>
-          <t>Se regresa a la pantalla de inicio del portal de pagos del Gobierno</t>
-        </is>
-      </c>
-      <c r="K54" s="70" t="n"/>
-      <c r="L54" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M54" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N54" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1" s="32">
+      <c r="B54" s="73" t="n"/>
+      <c r="C54" s="73" t="n"/>
+      <c r="D54" s="74" t="n"/>
+      <c r="E54" s="75" t="n"/>
+      <c r="F54" s="73" t="n"/>
+      <c r="G54" s="73" t="n"/>
+      <c r="H54" s="73" t="n"/>
+      <c r="I54" s="73" t="n"/>
+      <c r="J54" s="73" t="n"/>
+      <c r="K54" s="73" t="n"/>
+      <c r="L54" s="73" t="n"/>
+      <c r="M54" s="73" t="n"/>
+      <c r="N54" s="73" t="n"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="32">
       <c r="A55" s="73" t="inlineStr">
         <is>
           <t>TC-BP-032</t>
         </is>
       </c>
-      <c r="B55" s="73" t="inlineStr">
-        <is>
-          <t>07. Resultado Fallido y Reintento</t>
-        </is>
-      </c>
-      <c r="C55" s="73" t="inlineStr">
-        <is>
-          <t>Verificar la pantalla de 'Transaccion rechazada'</t>
-        </is>
-      </c>
-      <c r="D55" s="74" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E55" s="75" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F55" s="73" t="inlineStr">
-        <is>
-          <t>El pago fue enviado al banco y rechazado, o fue rechazado por el sistema antes de llegar al banco</t>
-        </is>
-      </c>
-      <c r="G55" s="73" t="inlineStr">
-        <is>
-          <t>Si - tarjeta 'Not authenticated' (el banco rechaza la autenticacion)</t>
-        </is>
-      </c>
-      <c r="H55" s="73" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar una tarjeta de prueba que el banco rechace y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Revisar la pantalla 'Transaccion rechazada' y el aviso emergente</t>
-        </is>
-      </c>
-      <c r="I55" s="73" t="inlineStr">
-        <is>
-          <t>VISA 4110 7600 0000 0065 / vencimiento futuro (ej. 12/30) / CVV 123 (alterna: MasterCard 5180 3000 0000 0039)</t>
-        </is>
-      </c>
-      <c r="J55" s="73" t="inlineStr">
-        <is>
-          <t>Se muestra 'Transaccion rechazada' con Estado y Codigo de respuesta, y el aviso 'Ha ocurrido un error al procesar el pago.'</t>
-        </is>
-      </c>
+      <c r="B55" s="73" t="n"/>
+      <c r="C55" s="73" t="n"/>
+      <c r="D55" s="74" t="n"/>
+      <c r="E55" s="75" t="n"/>
+      <c r="F55" s="73" t="n"/>
+      <c r="G55" s="73" t="n"/>
+      <c r="H55" s="73" t="n"/>
+      <c r="I55" s="73" t="n"/>
+      <c r="J55" s="73" t="n"/>
       <c r="K55" s="73" t="n"/>
-      <c r="L55" s="73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M55" s="73" t="inlineStr">
-        <is>
-          <t>[Act. 29/09/2026] Actualizado con las pantallas reales
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N55" s="73" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="L55" s="73" t="n"/>
+      <c r="M55" s="73" t="n"/>
+      <c r="N55" s="73" t="n"/>
     </row>
     <row r="56" ht="75" customHeight="1" s="32">
       <c r="A56" s="73" t="inlineStr">
@@ -6221,83 +5641,25 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="105" customHeight="1" s="32">
+    <row r="57" ht="15" customHeight="1" s="32">
       <c r="A57" s="73" t="inlineStr">
         <is>
           <t>TC-BP-034</t>
         </is>
       </c>
-      <c r="B57" s="73" t="inlineStr">
-        <is>
-          <t>07. Resultado Fallido y Reintento</t>
-        </is>
-      </c>
-      <c r="C57" s="73" t="inlineStr">
-        <is>
-          <t>Reintentar el pago con una tarjeta valida despues de un primer rechazo</t>
-        </is>
-      </c>
-      <c r="D57" s="74" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E57" s="75" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F57" s="73" t="inlineStr">
-        <is>
-          <t>Primer intento rechazado; boton 'Reintentar' presionado</t>
-        </is>
-      </c>
-      <c r="G57" s="73" t="inlineStr">
-        <is>
-          <t>Si - primero 'Not authenticated' y despues 'Not challenge'</t>
-        </is>
-      </c>
-      <c r="H57" s="73" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar una tarjeta de prueba que el banco rechace y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. En 'Transaccion rechazada' dar clic en 'Reintentar'
-7. Completar de nuevo los Pasos 1 a 3 con una tarjeta valida
-8. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-9. Si el banco lo solicita, completar la autenticacion 3D Secure en la pagina del banco
-10. Revisar el resultado
-11. (Manual) Ingresar a Citeling y verificar que el pago aparezca con la referencia, importe, autorizacion, fecha y tipo de pago</t>
-        </is>
-      </c>
-      <c r="I57" s="73" t="inlineStr">
-        <is>
-          <t>1er intento: VISA 4110 7600 0000 0065 / 2do intento: VISA 4111 1111 1111 1111</t>
-        </is>
-      </c>
-      <c r="J57" s="73" t="inlineStr">
-        <is>
-          <t>El segundo intento se aprueba, se muestra 'Transaccion aprobada' y en Citeling solo aparece un pago</t>
-        </is>
-      </c>
+      <c r="B57" s="73" t="n"/>
+      <c r="C57" s="73" t="n"/>
+      <c r="D57" s="74" t="n"/>
+      <c r="E57" s="75" t="n"/>
+      <c r="F57" s="73" t="n"/>
+      <c r="G57" s="73" t="n"/>
+      <c r="H57" s="73" t="n"/>
+      <c r="I57" s="73" t="n"/>
+      <c r="J57" s="73" t="n"/>
       <c r="K57" s="73" t="n"/>
-      <c r="L57" s="73" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M57" s="73" t="inlineStr">
-        <is>
-          <t>[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N57" s="73" t="inlineStr">
-        <is>
-          <t>Mixta (automatizada + Citeling manual)</t>
-        </is>
-      </c>
+      <c r="L57" s="73" t="n"/>
+      <c r="M57" s="73" t="n"/>
+      <c r="N57" s="73" t="n"/>
     </row>
     <row r="58" ht="75" customHeight="1" s="32">
       <c r="A58" s="73" t="inlineStr">
@@ -6372,78 +5734,25 @@
         </is>
       </c>
     </row>
-    <row r="59" ht="135" customHeight="1" s="32">
-      <c r="A59" s="70" t="inlineStr">
+    <row r="59" ht="15" customHeight="1" s="32">
+      <c r="A59" s="73" t="inlineStr">
         <is>
           <t>TC-BP-067</t>
         </is>
       </c>
-      <c r="B59" s="70" t="inlineStr">
-        <is>
-          <t>07. Resultado Fallido y Reintento</t>
-        </is>
-      </c>
-      <c r="C59" s="70" t="inlineStr">
-        <is>
-          <t>Verificar el detalle y el aviso emergente de una transaccion rechazada</t>
-        </is>
-      </c>
-      <c r="D59" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E59" s="72" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F59" s="70" t="inlineStr">
-        <is>
-          <t>El pago fue enviado y el resultado fue 'Transaccion rechazada'</t>
-        </is>
-      </c>
-      <c r="G59" s="70" t="inlineStr">
-        <is>
-          <t>Si - tarjeta 'Not authenticated' (el banco rechaza la autenticacion)</t>
-        </is>
-      </c>
-      <c r="H59" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar una tarjeta de prueba que el banco rechace y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Revisar el detalle de 'Transaccion rechazada' y el aviso emergente</t>
-        </is>
-      </c>
-      <c r="I59" s="70" t="inlineStr">
-        <is>
-          <t>VISA 4110 7600 0000 0065 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J59" s="70" t="inlineStr">
-        <is>
-          <t>Se muestran Estado, Codigo de respuesta, Referencia, Autorizacion e Identificador, y el aviso 'Ha ocurrido un error al procesar el pago.'</t>
-        </is>
-      </c>
-      <c r="K59" s="70" t="n"/>
-      <c r="L59" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M59" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] [Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N59" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="B59" s="73" t="n"/>
+      <c r="C59" s="73" t="n"/>
+      <c r="D59" s="74" t="n"/>
+      <c r="E59" s="75" t="n"/>
+      <c r="F59" s="73" t="n"/>
+      <c r="G59" s="73" t="n"/>
+      <c r="H59" s="73" t="n"/>
+      <c r="I59" s="73" t="n"/>
+      <c r="J59" s="73" t="n"/>
+      <c r="K59" s="73" t="n"/>
+      <c r="L59" s="73" t="n"/>
+      <c r="M59" s="73" t="n"/>
+      <c r="N59" s="73" t="n"/>
     </row>
     <row r="60" ht="105" customHeight="1" s="32">
       <c r="A60" s="70" t="inlineStr">
@@ -6521,79 +5830,25 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="75" customHeight="1" s="32">
-      <c r="A61" s="70" t="inlineStr">
+    <row r="61" ht="15" customHeight="1" s="32">
+      <c r="A61" s="73" t="inlineStr">
         <is>
           <t>TC-BP-069</t>
         </is>
       </c>
-      <c r="B61" s="70" t="inlineStr">
-        <is>
-          <t>07. Resultado Fallido y Reintento</t>
-        </is>
-      </c>
-      <c r="C61" s="70" t="inlineStr">
-        <is>
-          <t>Verificar que los textos de la pantalla de rechazo sean claros y consistentes</t>
-        </is>
-      </c>
-      <c r="D61" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E61" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F61" s="70" t="inlineStr">
-        <is>
-          <t>El pago fue enviado y el resultado fue 'Transaccion rechazada'</t>
-        </is>
-      </c>
-      <c r="G61" s="70" t="inlineStr">
-        <is>
-          <t>Si - tarjeta 'Not authenticated' (el banco rechaza la autenticacion)</t>
-        </is>
-      </c>
-      <c r="H61" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar una tarjeta de prueba que el banco rechace y dar clic en 'Continuar'
-5. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-6. Revisar titulo, subtitulo y estado de la pantalla de rechazo</t>
-        </is>
-      </c>
-      <c r="I61" s="70" t="inlineStr">
-        <is>
-          <t>VISA 4110 7600 0000 0065 / vencimiento futuro (ej. 12/30) / CVV 123</t>
-        </is>
-      </c>
-      <c r="J61" s="70" t="inlineStr">
-        <is>
-          <t>Los textos estan en espanol, son comprensibles y no se contradicen con el resultado</t>
-        </is>
-      </c>
-      <c r="K61" s="70" t="n"/>
-      <c r="L61" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M61" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Observado: 'Transaccion rechazada' con subtitulo 'Payment verificado.' / 'Payout realizado.' y estado 'Invalid arguments...' en ingles
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N61" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="B61" s="73" t="n"/>
+      <c r="C61" s="73" t="n"/>
+      <c r="D61" s="74" t="n"/>
+      <c r="E61" s="75" t="n"/>
+      <c r="F61" s="73" t="n"/>
+      <c r="G61" s="73" t="n"/>
+      <c r="H61" s="73" t="n"/>
+      <c r="I61" s="73" t="n"/>
+      <c r="J61" s="73" t="n"/>
+      <c r="K61" s="73" t="n"/>
+      <c r="L61" s="73" t="n"/>
+      <c r="M61" s="73" t="n"/>
+      <c r="N61" s="73" t="n"/>
     </row>
     <row r="62" ht="105" customHeight="1" s="32">
       <c r="A62" s="70" t="inlineStr">
@@ -7825,79 +7080,25 @@
         </is>
       </c>
     </row>
-    <row r="79" ht="75" customHeight="1" s="32">
-      <c r="A79" s="70" t="inlineStr">
+    <row r="79" ht="15" customHeight="1" s="32">
+      <c r="A79" s="73" t="inlineStr">
         <is>
           <t>TC-BP-066</t>
         </is>
       </c>
-      <c r="B79" s="70" t="inlineStr">
-        <is>
-          <t>10. Paso 4 - Confirmacion antes de pagar</t>
-        </is>
-      </c>
-      <c r="C79" s="70" t="inlineStr">
-        <is>
-          <t>Navegar entre pasos con los numeros del indicador superior</t>
-        </is>
-      </c>
-      <c r="D79" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E79" s="72" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F79" s="70" t="inlineStr">
-        <is>
-          <t>Los Pasos 1, 2 y 3 fueron completados; se muestra el Paso 4 - 'Revisa tu informacion antes de pagar'</t>
-        </is>
-      </c>
-      <c r="G79" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H79" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
-5. Paso 4: dar clic en el numero '1' del indicador superior
-6. Revisar si cambia de paso y si conserva los datos</t>
-        </is>
-      </c>
-      <c r="I79" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J79" s="70" t="inlineStr">
-        <is>
-          <t>La navegacion no pierde datos ni permite saltarse validaciones</t>
-        </is>
-      </c>
-      <c r="K79" s="70" t="n"/>
-      <c r="L79" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M79" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] [Act. 29/09/2026] Observado: los numeros del indicador de pasos son solo informativos (no navegan aunque son botones). Confirmar con diseno si debe permitir navegar
-[Revision 29/09/2026] Pasos actualizados al flujo real (referencia / linea de captura)</t>
-        </is>
-      </c>
-      <c r="N79" s="70" t="inlineStr">
-        <is>
-          <t>Automatizada</t>
-        </is>
-      </c>
+      <c r="B79" s="73" t="n"/>
+      <c r="C79" s="73" t="n"/>
+      <c r="D79" s="74" t="n"/>
+      <c r="E79" s="75" t="n"/>
+      <c r="F79" s="73" t="n"/>
+      <c r="G79" s="73" t="n"/>
+      <c r="H79" s="73" t="n"/>
+      <c r="I79" s="73" t="n"/>
+      <c r="J79" s="73" t="n"/>
+      <c r="K79" s="73" t="n"/>
+      <c r="L79" s="73" t="n"/>
+      <c r="M79" s="73" t="n"/>
+      <c r="N79" s="73" t="n"/>
     </row>
     <row r="80" ht="135" customHeight="1" s="32">
       <c r="A80" s="70" t="inlineStr">
@@ -8054,78 +7255,25 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="75" customHeight="1" s="32">
-      <c r="A82" s="70" t="inlineStr">
+    <row r="82" ht="15" customHeight="1" s="32">
+      <c r="A82" s="73" t="inlineStr">
         <is>
           <t>TC-BP-087</t>
         </is>
       </c>
-      <c r="B82" s="70" t="inlineStr">
-        <is>
-          <t>11. Meses Sin Intereses (MSI)</t>
-        </is>
-      </c>
-      <c r="C82" s="70" t="inlineStr">
-        <is>
-          <t>Verificar que el unico plazo ofrecido sea 6 meses</t>
-        </is>
-      </c>
-      <c r="D82" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E82" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F82" s="70" t="inlineStr">
-        <is>
-          <t>Referencia con meses sin intereses activo</t>
-        </is>
-      </c>
-      <c r="G82" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H82" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
-5. Paso 4: revisar las opciones de meses mostradas (solo debe aparecer 6 meses)</t>
-        </is>
-      </c>
-      <c r="I82" s="70" t="inlineStr">
-        <is>
-          <t>Plazo configurado: 6 meses</t>
-        </is>
-      </c>
-      <c r="J82" s="70" t="inlineStr">
-        <is>
-          <t>Solo se ofrece la opcion de 6 meses sin intereses (ademas de pagar de contado)</t>
-        </is>
-      </c>
-      <c r="K82" s="70" t="n"/>
-      <c r="L82" s="70" t="inlineStr">
-        <is>
-          <t>Bloqueado</t>
-        </is>
-      </c>
-      <c r="M82" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]
-[Revision 29/09/2026] Bloqueado: la opcion de meses sin intereses aun no esta habilitada; el unico plazo sera 6 meses</t>
-        </is>
-      </c>
-      <c r="N82" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar (bloqueado: MSI no habilitado)</t>
-        </is>
-      </c>
+      <c r="B82" s="73" t="n"/>
+      <c r="C82" s="73" t="n"/>
+      <c r="D82" s="74" t="n"/>
+      <c r="E82" s="75" t="n"/>
+      <c r="F82" s="73" t="n"/>
+      <c r="G82" s="73" t="n"/>
+      <c r="H82" s="73" t="n"/>
+      <c r="I82" s="73" t="n"/>
+      <c r="J82" s="73" t="n"/>
+      <c r="K82" s="73" t="n"/>
+      <c r="L82" s="73" t="n"/>
+      <c r="M82" s="73" t="n"/>
+      <c r="N82" s="73" t="n"/>
     </row>
     <row r="83" ht="105" customHeight="1" s="32">
       <c r="A83" s="70" t="inlineStr">
@@ -8422,81 +7570,25 @@
         </is>
       </c>
     </row>
-    <row r="87" ht="75" customHeight="1" s="32">
-      <c r="A87" s="70" t="inlineStr">
+    <row r="87" ht="15" customHeight="1" s="32">
+      <c r="A87" s="73" t="inlineStr">
         <is>
           <t>TC-BP-092</t>
         </is>
       </c>
-      <c r="B87" s="70" t="inlineStr">
-        <is>
-          <t>12. Importes menores a $1,000</t>
-        </is>
-      </c>
-      <c r="C87" s="70" t="inlineStr">
-        <is>
-          <t>Importes limite: $999.99 y $1.00</t>
-        </is>
-      </c>
-      <c r="D87" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E87" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F87" s="70" t="inlineStr">
-        <is>
-          <t>Referencias con importe de $999.99 y de $1.00</t>
-        </is>
-      </c>
-      <c r="G87" s="70" t="inlineStr">
-        <is>
-          <t>No - tarjeta 'Not challenge' (se aprueba sin reto)</t>
-        </is>
-      </c>
-      <c r="H87" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3 - Datos de Tarjeta: capturar nombre, apellido, numero de tarjeta, vencimiento y CVV validos y dar clic en 'Continuar'
-5. Paso 4: verificar el importe mostrado
-6. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-7. Si el banco lo solicita, completar la autenticacion 3D Secure en la pagina del banco
-8. Revisar el resultado
-9. (Manual) Ingresar a Citeling y verificar que el pago aparezca con la referencia, importe, autorizacion, fecha y tipo de pago</t>
-        </is>
-      </c>
-      <c r="I87" s="70" t="inlineStr">
-        <is>
-          <t>Importes: $999.99 / $1.00 / VISA 4111 1111 1111 1111</t>
-        </is>
-      </c>
-      <c r="J87" s="70" t="inlineStr">
-        <is>
-          <t>Los importes se muestran con 2 decimales y se cobra exactamente el monto de la referencia</t>
-        </is>
-      </c>
-      <c r="K87" s="70" t="n"/>
-      <c r="L87" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M87" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N87" s="70" t="inlineStr">
-        <is>
-          <t>Mixta (automatizada + Citeling manual)</t>
-        </is>
-      </c>
+      <c r="B87" s="73" t="n"/>
+      <c r="C87" s="73" t="n"/>
+      <c r="D87" s="74" t="n"/>
+      <c r="E87" s="75" t="n"/>
+      <c r="F87" s="73" t="n"/>
+      <c r="G87" s="73" t="n"/>
+      <c r="H87" s="73" t="n"/>
+      <c r="I87" s="73" t="n"/>
+      <c r="J87" s="73" t="n"/>
+      <c r="K87" s="73" t="n"/>
+      <c r="L87" s="73" t="n"/>
+      <c r="M87" s="73" t="n"/>
+      <c r="N87" s="73" t="n"/>
     </row>
     <row r="88" ht="75" customHeight="1" s="32">
       <c r="A88" s="70" t="inlineStr">
@@ -8569,150 +7661,45 @@
         </is>
       </c>
     </row>
-    <row r="89" ht="75" customHeight="1" s="32">
-      <c r="A89" s="70" t="inlineStr">
+    <row r="89" ht="15" customHeight="1" s="32">
+      <c r="A89" s="73" t="inlineStr">
         <is>
           <t>TC-BP-071</t>
         </is>
       </c>
-      <c r="B89" s="70" t="inlineStr">
-        <is>
-          <t>13. Datos No Existentes y Reintentar</t>
-        </is>
-      </c>
-      <c r="C89" s="70" t="inlineStr">
-        <is>
-          <t>Capturar una linea de captura que no existe</t>
-        </is>
-      </c>
-      <c r="D89" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E89" s="72" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F89" s="70" t="inlineStr">
-        <is>
-          <t>Portal de pagos del Gobierno en 'Pago de predial'</t>
-        </is>
-      </c>
-      <c r="G89" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H89" s="70" t="inlineStr">
-        <is>
-          <t>1. Entrar al portal &gt; 'Predial'
-2. Capturar una linea de captura de 24 digitos que no existe
-3. Capturar el captcha y dar clic en 'Consultar'
-4. Revisar el mensaje y volver a intentar con una linea de captura valida</t>
-        </is>
-      </c>
-      <c r="I89" s="70" t="inlineStr">
-        <is>
-          <t>Linea de captura inexistente</t>
-        </is>
-      </c>
-      <c r="J89" s="70" t="inlineStr">
-        <is>
-          <t>Se muestra un mensaje claro de linea de captura no encontrada, no se permite pagar y se puede corregir e intentar de nuevo</t>
-        </is>
-      </c>
-      <c r="K89" s="70" t="n"/>
-      <c r="L89" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M89" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N89" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="75" customHeight="1" s="32">
-      <c r="A90" s="70" t="inlineStr">
+      <c r="B89" s="73" t="n"/>
+      <c r="C89" s="73" t="n"/>
+      <c r="D89" s="74" t="n"/>
+      <c r="E89" s="75" t="n"/>
+      <c r="F89" s="73" t="n"/>
+      <c r="G89" s="73" t="n"/>
+      <c r="H89" s="73" t="n"/>
+      <c r="I89" s="73" t="n"/>
+      <c r="J89" s="73" t="n"/>
+      <c r="K89" s="73" t="n"/>
+      <c r="L89" s="73" t="n"/>
+      <c r="M89" s="73" t="n"/>
+      <c r="N89" s="73" t="n"/>
+    </row>
+    <row r="90" ht="15" customHeight="1" s="32">
+      <c r="A90" s="73" t="inlineStr">
         <is>
           <t>TC-BP-072</t>
         </is>
       </c>
-      <c r="B90" s="70" t="inlineStr">
-        <is>
-          <t>13. Datos No Existentes y Reintentar</t>
-        </is>
-      </c>
-      <c r="C90" s="70" t="inlineStr">
-        <is>
-          <t>Pagar con una tarjeta con formato valido pero que no existe</t>
-        </is>
-      </c>
-      <c r="D90" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E90" s="72" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="F90" s="70" t="inlineStr">
-        <is>
-          <t>Los Pasos 1 y 2 fueron completados correctamente</t>
-        </is>
-      </c>
-      <c r="G90" s="70" t="inlineStr">
-        <is>
-          <t>Depende del banco</t>
-        </is>
-      </c>
-      <c r="H90" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3: capturar una tarjeta de 16 digitos con formato valido que no existe y el resto de datos validos
-5. Dar clic en 'Continuar'
-6. Paso 4 - Pago: revisar el resumen y dar clic en 'Continuar' para pagar
-7. Revisar el resultado y el boton 'Reintentar'</t>
-        </is>
-      </c>
-      <c r="I90" s="70" t="inlineStr">
-        <is>
-          <t>Tarjeta inexistente (formato valido)</t>
-        </is>
-      </c>
-      <c r="J90" s="70" t="inlineStr">
-        <is>
-          <t>Se muestra 'Transaccion rechazada' con un mensaje comprensible y el boton 'Reintentar' disponible; no se registra cobro</t>
-        </is>
-      </c>
-      <c r="K90" s="70" t="n"/>
-      <c r="L90" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M90" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N90" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
+      <c r="B90" s="73" t="n"/>
+      <c r="C90" s="73" t="n"/>
+      <c r="D90" s="74" t="n"/>
+      <c r="E90" s="75" t="n"/>
+      <c r="F90" s="73" t="n"/>
+      <c r="G90" s="73" t="n"/>
+      <c r="H90" s="73" t="n"/>
+      <c r="I90" s="73" t="n"/>
+      <c r="J90" s="73" t="n"/>
+      <c r="K90" s="73" t="n"/>
+      <c r="L90" s="73" t="n"/>
+      <c r="M90" s="73" t="n"/>
+      <c r="N90" s="73" t="n"/>
     </row>
     <row r="91" ht="75" customHeight="1" s="32">
       <c r="A91" s="70" t="inlineStr">
@@ -8788,787 +7775,225 @@
         </is>
       </c>
     </row>
-    <row r="92" ht="75" customHeight="1" s="32">
-      <c r="A92" s="70" t="inlineStr">
+    <row r="92" ht="15" customHeight="1" s="32">
+      <c r="A92" s="73" t="inlineStr">
         <is>
           <t>TC-BP-074</t>
         </is>
       </c>
-      <c r="B92" s="70" t="inlineStr">
-        <is>
-          <t>13. Datos No Existentes y Reintentar</t>
-        </is>
-      </c>
-      <c r="C92" s="70" t="inlineStr">
-        <is>
-          <t>Capturar un codigo postal que no corresponde al Estado seleccionado</t>
-        </is>
-      </c>
-      <c r="D92" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E92" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F92" s="70" t="inlineStr">
-        <is>
-          <t>El Paso 1 - Contacto fue completado y confirmado correctamente</t>
-        </is>
-      </c>
-      <c r="G92" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H92" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2: escribir Codigo Postal '01000' (Ciudad de Mexico) y seleccionar Estado 'Puebla'
-4. Dar clic en 'Continuar'</t>
-        </is>
-      </c>
-      <c r="I92" s="70" t="inlineStr">
-        <is>
-          <t>CP: 01000 / Estado: Puebla</t>
-        </is>
-      </c>
-      <c r="J92" s="70" t="inlineStr">
-        <is>
-          <t>El sistema avisa que el codigo postal no corresponde al estado o documenta que no hace esta validacion</t>
-        </is>
-      </c>
-      <c r="K92" s="70" t="n"/>
-      <c r="L92" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M92" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N92" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="75" customHeight="1" s="32">
-      <c r="A93" s="70" t="inlineStr">
+      <c r="B92" s="73" t="n"/>
+      <c r="C92" s="73" t="n"/>
+      <c r="D92" s="74" t="n"/>
+      <c r="E92" s="75" t="n"/>
+      <c r="F92" s="73" t="n"/>
+      <c r="G92" s="73" t="n"/>
+      <c r="H92" s="73" t="n"/>
+      <c r="I92" s="73" t="n"/>
+      <c r="J92" s="73" t="n"/>
+      <c r="K92" s="73" t="n"/>
+      <c r="L92" s="73" t="n"/>
+      <c r="M92" s="73" t="n"/>
+      <c r="N92" s="73" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1" s="32">
+      <c r="A93" s="73" t="inlineStr">
         <is>
           <t>TC-BP-075</t>
         </is>
       </c>
-      <c r="B93" s="70" t="inlineStr">
-        <is>
-          <t>13. Datos No Existentes y Reintentar</t>
-        </is>
-      </c>
-      <c r="C93" s="70" t="inlineStr">
-        <is>
-          <t>Capturar una ciudad que no existe en el Estado seleccionado</t>
-        </is>
-      </c>
-      <c r="D93" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E93" s="72" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F93" s="70" t="inlineStr">
-        <is>
-          <t>El Paso 1 - Contacto fue completado y confirmado correctamente</t>
-        </is>
-      </c>
-      <c r="G93" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H93" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2: escribir Ciudad 'Xyzabc' con Estado 'Puebla' y el resto valido
-4. Dar clic en 'Continuar'</t>
-        </is>
-      </c>
-      <c r="I93" s="70" t="inlineStr">
-        <is>
-          <t>Ciudad: Xyzabc</t>
-        </is>
-      </c>
-      <c r="J93" s="70" t="inlineStr">
-        <is>
-          <t>El sistema valida la ciudad contra el estado o documenta que acepta texto libre sin afectar el pago</t>
-        </is>
-      </c>
-      <c r="K93" s="70" t="n"/>
-      <c r="L93" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M93" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N93" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="90" customHeight="1" s="32">
-      <c r="A94" s="70" t="inlineStr">
+      <c r="B93" s="73" t="n"/>
+      <c r="C93" s="73" t="n"/>
+      <c r="D93" s="74" t="n"/>
+      <c r="E93" s="75" t="n"/>
+      <c r="F93" s="73" t="n"/>
+      <c r="G93" s="73" t="n"/>
+      <c r="H93" s="73" t="n"/>
+      <c r="I93" s="73" t="n"/>
+      <c r="J93" s="73" t="n"/>
+      <c r="K93" s="73" t="n"/>
+      <c r="L93" s="73" t="n"/>
+      <c r="M93" s="73" t="n"/>
+      <c r="N93" s="73" t="n"/>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="32">
+      <c r="A94" s="73" t="inlineStr">
         <is>
           <t>TC-BP-076</t>
         </is>
       </c>
-      <c r="B94" s="70" t="inlineStr">
-        <is>
-          <t>13. Datos No Existentes y Reintentar</t>
-        </is>
-      </c>
-      <c r="C94" s="70" t="inlineStr">
-        <is>
-          <t>Capturar un correo con dominio que no existe</t>
-        </is>
-      </c>
-      <c r="D94" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E94" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F94" s="70" t="inlineStr">
-        <is>
-          <t>Se ingreso con una referencia o linea de captura vigente y se muestra el Paso 1 - Contacto</t>
-        </is>
-      </c>
-      <c r="G94" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H94" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Capturar el correo 'contribuyente@dominioquenoexiste123.mx'
-3. Dar clic en 'Continuar' y completar el pago</t>
-        </is>
-      </c>
-      <c r="I94" s="70" t="inlineStr">
-        <is>
-          <t>Correo: contribuyente@dominioquenoexiste123.mx</t>
-        </is>
-      </c>
-      <c r="J94" s="70" t="inlineStr">
-        <is>
-          <t>El sistema advierte que el correo podria no ser valido o se documenta que el comprobante no se entrega; el pago no se ve afectado</t>
-        </is>
-      </c>
-      <c r="K94" s="70" t="n"/>
-      <c r="L94" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M94" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N94" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="75" customHeight="1" s="32">
-      <c r="A95" s="70" t="inlineStr">
+      <c r="B94" s="73" t="n"/>
+      <c r="C94" s="73" t="n"/>
+      <c r="D94" s="74" t="n"/>
+      <c r="E94" s="75" t="n"/>
+      <c r="F94" s="73" t="n"/>
+      <c r="G94" s="73" t="n"/>
+      <c r="H94" s="73" t="n"/>
+      <c r="I94" s="73" t="n"/>
+      <c r="J94" s="73" t="n"/>
+      <c r="K94" s="73" t="n"/>
+      <c r="L94" s="73" t="n"/>
+      <c r="M94" s="73" t="n"/>
+      <c r="N94" s="73" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1" s="32">
+      <c r="A95" s="73" t="inlineStr">
         <is>
           <t>TC-BP-077</t>
         </is>
       </c>
-      <c r="B95" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C95" s="70" t="inlineStr">
-        <is>
-          <t>Formato del telefono: mascara, solo numeros y de 10 a 13 digitos</t>
-        </is>
-      </c>
-      <c r="D95" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E95" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F95" s="70" t="inlineStr">
-        <is>
-          <t>Se ingreso con una referencia o linea de captura vigente y se muestra el Paso 1 - Contacto</t>
-        </is>
-      </c>
-      <c r="G95" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H95" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Escribir 10 digitos y revisar la mascara aplicada
-3. Escribir letras y simbolos y revisar si se aceptan
-4. Regresar desde el Paso 2 y revisar el formato mostrado</t>
-        </is>
-      </c>
-      <c r="I95" s="70" t="inlineStr">
-        <is>
-          <t>5540076333 / abc#$</t>
-        </is>
-      </c>
-      <c r="J95" s="70" t="inlineStr">
-        <is>
-          <t>El telefono se muestra con la mascara '(55) 1234-5678', solo acepta numeros y de 10 a 13 digitos</t>
-        </is>
-      </c>
-      <c r="K95" s="70" t="n"/>
-      <c r="L95" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M95" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Observado: al regresar se muestra '(5540) 076-333'</t>
-        </is>
-      </c>
-      <c r="N95" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="70" t="inlineStr">
+      <c r="B95" s="73" t="n"/>
+      <c r="C95" s="73" t="n"/>
+      <c r="D95" s="74" t="n"/>
+      <c r="E95" s="75" t="n"/>
+      <c r="F95" s="73" t="n"/>
+      <c r="G95" s="73" t="n"/>
+      <c r="H95" s="73" t="n"/>
+      <c r="I95" s="73" t="n"/>
+      <c r="J95" s="73" t="n"/>
+      <c r="K95" s="73" t="n"/>
+      <c r="L95" s="73" t="n"/>
+      <c r="M95" s="73" t="n"/>
+      <c r="N95" s="73" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1" s="32">
+      <c r="A96" s="73" t="inlineStr">
         <is>
           <t>TC-BP-078</t>
         </is>
       </c>
-      <c r="B96" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C96" s="70" t="inlineStr">
-        <is>
-          <t>Formato del correo: longitud maxima y caracteres permitidos</t>
-        </is>
-      </c>
-      <c r="D96" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E96" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F96" s="70" t="inlineStr">
-        <is>
-          <t>Se ingreso con una referencia o linea de captura vigente y se muestra el Paso 1 - Contacto</t>
-        </is>
-      </c>
-      <c r="G96" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H96" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Escribir un correo valido de 31 caracteres o mas
-3. Dar clic en 'Continuar'</t>
-        </is>
-      </c>
-      <c r="I96" s="70" t="inlineStr">
-        <is>
-          <t>Correo de 31+ caracteres</t>
-        </is>
-      </c>
-      <c r="J96" s="70" t="inlineStr">
-        <is>
-          <t>El sistema limita o valida la longitud maxima del correo (30 caracteres segun documento, campo val_7)</t>
-        </is>
-      </c>
-      <c r="K96" s="70" t="n"/>
-      <c r="L96" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M96" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N96" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="70" t="inlineStr">
+      <c r="B96" s="73" t="n"/>
+      <c r="C96" s="73" t="n"/>
+      <c r="D96" s="74" t="n"/>
+      <c r="E96" s="75" t="n"/>
+      <c r="F96" s="73" t="n"/>
+      <c r="G96" s="73" t="n"/>
+      <c r="H96" s="73" t="n"/>
+      <c r="I96" s="73" t="n"/>
+      <c r="J96" s="73" t="n"/>
+      <c r="K96" s="73" t="n"/>
+      <c r="L96" s="73" t="n"/>
+      <c r="M96" s="73" t="n"/>
+      <c r="N96" s="73" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1" s="32">
+      <c r="A97" s="73" t="inlineStr">
         <is>
           <t>TC-BP-079</t>
         </is>
       </c>
-      <c r="B97" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C97" s="70" t="inlineStr">
-        <is>
-          <t>Formato del codigo postal: solo numeros y exactamente 5 digitos</t>
-        </is>
-      </c>
-      <c r="D97" s="71" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="E97" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F97" s="70" t="inlineStr">
-        <is>
-          <t>El Paso 1 - Contacto fue completado y confirmado correctamente</t>
-        </is>
-      </c>
-      <c r="G97" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H97" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2: escribir letras y simbolos en Codigo Postal
-4. Escribir 6 digitos
-5. Revisar lo que queda escrito</t>
-        </is>
-      </c>
-      <c r="I97" s="70" t="inlineStr">
-        <is>
-          <t>CP: abc#1 / 123456</t>
-        </is>
-      </c>
-      <c r="J97" s="70" t="inlineStr">
-        <is>
-          <t>El campo solo acepta numeros y como maximo 5 digitos</t>
-        </is>
-      </c>
-      <c r="K97" s="70" t="n"/>
-      <c r="L97" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M97" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N97" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="70" t="inlineStr">
+      <c r="B97" s="73" t="n"/>
+      <c r="C97" s="73" t="n"/>
+      <c r="D97" s="74" t="n"/>
+      <c r="E97" s="75" t="n"/>
+      <c r="F97" s="73" t="n"/>
+      <c r="G97" s="73" t="n"/>
+      <c r="H97" s="73" t="n"/>
+      <c r="I97" s="73" t="n"/>
+      <c r="J97" s="73" t="n"/>
+      <c r="K97" s="73" t="n"/>
+      <c r="L97" s="73" t="n"/>
+      <c r="M97" s="73" t="n"/>
+      <c r="N97" s="73" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1" s="32">
+      <c r="A98" s="73" t="inlineStr">
         <is>
           <t>TC-BP-080</t>
         </is>
       </c>
-      <c r="B98" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C98" s="70" t="inlineStr">
-        <is>
-          <t>Formato de calle y ciudad: caracteres permitidos y longitud maxima</t>
-        </is>
-      </c>
-      <c r="D98" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E98" s="72" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F98" s="70" t="inlineStr">
-        <is>
-          <t>El Paso 1 - Contacto fue completado y confirmado correctamente</t>
-        </is>
-      </c>
-      <c r="G98" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H98" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2: escribir textos muy largos (100+ caracteres) en Calle y Ciudad
-4. Revisar si se limitan y como se muestran en el resumen</t>
-        </is>
-      </c>
-      <c r="I98" s="70" t="inlineStr">
-        <is>
-          <t>Calle/Ciudad de 100+ caracteres</t>
-        </is>
-      </c>
-      <c r="J98" s="70" t="inlineStr">
-        <is>
-          <t>Los campos limitan la longitud o validan con un mensaje claro; el resumen del Paso 4 no se desacomoda</t>
-        </is>
-      </c>
-      <c r="K98" s="70" t="n"/>
-      <c r="L98" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M98" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N98" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="70" t="inlineStr">
+      <c r="B98" s="73" t="n"/>
+      <c r="C98" s="73" t="n"/>
+      <c r="D98" s="74" t="n"/>
+      <c r="E98" s="75" t="n"/>
+      <c r="F98" s="73" t="n"/>
+      <c r="G98" s="73" t="n"/>
+      <c r="H98" s="73" t="n"/>
+      <c r="I98" s="73" t="n"/>
+      <c r="J98" s="73" t="n"/>
+      <c r="K98" s="73" t="n"/>
+      <c r="L98" s="73" t="n"/>
+      <c r="M98" s="73" t="n"/>
+      <c r="N98" s="73" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1" s="32">
+      <c r="A99" s="73" t="inlineStr">
         <is>
           <t>TC-BP-081</t>
         </is>
       </c>
-      <c r="B99" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C99" s="70" t="inlineStr">
-        <is>
-          <t>Formato de nombre y apellido: solo letras y longitud maxima</t>
-        </is>
-      </c>
-      <c r="D99" s="71" t="inlineStr">
-        <is>
-          <t>ESPECIAL</t>
-        </is>
-      </c>
-      <c r="E99" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F99" s="70" t="inlineStr">
-        <is>
-          <t>Los Pasos 1 (Contacto) y 2 (Direccion) fueron completados y confirmados correctamente</t>
-        </is>
-      </c>
-      <c r="G99" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H99" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3: escribir un nombre y apellido que juntos superen 50 caracteres
-5. Dar clic en 'Continuar'</t>
-        </is>
-      </c>
-      <c r="I99" s="70" t="inlineStr">
-        <is>
-          <t>Nombre + apellido de 50+ caracteres</t>
-        </is>
-      </c>
-      <c r="J99" s="70" t="inlineStr">
-        <is>
-          <t>El sistema limita o valida la longitud (s_nombre acepta 50 caracteres segun documento)</t>
-        </is>
-      </c>
-      <c r="K99" s="70" t="n"/>
-      <c r="L99" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M99" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N99" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="70" t="inlineStr">
+      <c r="B99" s="73" t="n"/>
+      <c r="C99" s="73" t="n"/>
+      <c r="D99" s="74" t="n"/>
+      <c r="E99" s="75" t="n"/>
+      <c r="F99" s="73" t="n"/>
+      <c r="G99" s="73" t="n"/>
+      <c r="H99" s="73" t="n"/>
+      <c r="I99" s="73" t="n"/>
+      <c r="J99" s="73" t="n"/>
+      <c r="K99" s="73" t="n"/>
+      <c r="L99" s="73" t="n"/>
+      <c r="M99" s="73" t="n"/>
+      <c r="N99" s="73" t="n"/>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="32">
+      <c r="A100" s="73" t="inlineStr">
         <is>
           <t>TC-BP-082</t>
         </is>
       </c>
-      <c r="B100" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C100" s="70" t="inlineStr">
-        <is>
-          <t>Formato del numero de tarjeta: solo numeros agrupados de 4 en 4</t>
-        </is>
-      </c>
-      <c r="D100" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E100" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F100" s="70" t="inlineStr">
-        <is>
-          <t>Los Pasos 1 (Contacto) y 2 (Direccion) fueron completados y confirmados correctamente</t>
-        </is>
-      </c>
-      <c r="G100" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H100" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3: escribir letras y simbolos en Numero de Tarjeta
-5. Escribir 16 digitos y revisar la agrupacion</t>
-        </is>
-      </c>
-      <c r="I100" s="70" t="inlineStr">
-        <is>
-          <t>abc#$ / 16 digitos</t>
-        </is>
-      </c>
-      <c r="J100" s="70" t="inlineStr">
-        <is>
-          <t>Solo acepta numeros, agrupa como '0000 0000 0000 0000' y acepta 15 o 16 digitos</t>
-        </is>
-      </c>
-      <c r="K100" s="70" t="n"/>
-      <c r="L100" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M100" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N100" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="70" t="inlineStr">
+      <c r="B100" s="73" t="n"/>
+      <c r="C100" s="73" t="n"/>
+      <c r="D100" s="74" t="n"/>
+      <c r="E100" s="75" t="n"/>
+      <c r="F100" s="73" t="n"/>
+      <c r="G100" s="73" t="n"/>
+      <c r="H100" s="73" t="n"/>
+      <c r="I100" s="73" t="n"/>
+      <c r="J100" s="73" t="n"/>
+      <c r="K100" s="73" t="n"/>
+      <c r="L100" s="73" t="n"/>
+      <c r="M100" s="73" t="n"/>
+      <c r="N100" s="73" t="n"/>
+    </row>
+    <row r="101" ht="15" customHeight="1" s="32">
+      <c r="A101" s="73" t="inlineStr">
         <is>
           <t>TC-BP-083</t>
         </is>
       </c>
-      <c r="B101" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C101" s="70" t="inlineStr">
-        <is>
-          <t>Formato del vencimiento: MM/AA con diagonal automatica</t>
-        </is>
-      </c>
-      <c r="D101" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E101" s="72" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="F101" s="70" t="inlineStr">
-        <is>
-          <t>Los Pasos 1 (Contacto) y 2 (Direccion) fueron completados y confirmados correctamente</t>
-        </is>
-      </c>
-      <c r="G101" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H101" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Paso 1 - Contacto: capturar telefono y correo validos y dar clic en 'Continuar'
-3. Paso 2 - Direccion: capturar calle, codigo postal, ciudad, pais y estado validos y dar clic en 'Continuar'
-4. Paso 3: escribir '1226' en Vencimiento
-5. Revisar que se muestre '12/26'
-6. Escribir letras y revisar si se aceptan</t>
-        </is>
-      </c>
-      <c r="I101" s="70" t="inlineStr">
-        <is>
-          <t>1226 / abc</t>
-        </is>
-      </c>
-      <c r="J101" s="70" t="inlineStr">
-        <is>
-          <t>Se muestra '12/26', solo acepta numeros y el mes debe estar entre 01 y 12</t>
-        </is>
-      </c>
-      <c r="K101" s="70" t="n"/>
-      <c r="L101" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M101" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO]</t>
-        </is>
-      </c>
-      <c r="N101" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="70" t="inlineStr">
+      <c r="B101" s="73" t="n"/>
+      <c r="C101" s="73" t="n"/>
+      <c r="D101" s="74" t="n"/>
+      <c r="E101" s="75" t="n"/>
+      <c r="F101" s="73" t="n"/>
+      <c r="G101" s="73" t="n"/>
+      <c r="H101" s="73" t="n"/>
+      <c r="I101" s="73" t="n"/>
+      <c r="J101" s="73" t="n"/>
+      <c r="K101" s="73" t="n"/>
+      <c r="L101" s="73" t="n"/>
+      <c r="M101" s="73" t="n"/>
+      <c r="N101" s="73" t="n"/>
+    </row>
+    <row r="102" ht="15" customHeight="1" s="32">
+      <c r="A102" s="73" t="inlineStr">
         <is>
           <t>TC-BP-084</t>
         </is>
       </c>
-      <c r="B102" s="70" t="inlineStr">
-        <is>
-          <t>14. Formatos de Campos</t>
-        </is>
-      </c>
-      <c r="C102" s="70" t="inlineStr">
-        <is>
-          <t>Formato del importe: moneda con separador de miles y 2 decimales</t>
-        </is>
-      </c>
-      <c r="D102" s="71" t="inlineStr">
-        <is>
-          <t>EXITO</t>
-        </is>
-      </c>
-      <c r="E102" s="72" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="F102" s="70" t="inlineStr">
-        <is>
-          <t>Se ingreso con una referencia o linea de captura vigente y se muestra el Paso 1 - Contacto</t>
-        </is>
-      </c>
-      <c r="G102" s="70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="H102" s="70" t="inlineStr">
-        <is>
-          <t>1. Ingresar con la referencia o linea de captura (hoja 'Flujo Real', pasos 1 a 5) hasta ver el Paso 1 - Contacto
-2. Revisar el importe del encabezado en los Pasos 1 a 4 y en el resultado</t>
-        </is>
-      </c>
-      <c r="I102" s="70" t="inlineStr">
-        <is>
-          <t>Importe: $2,280.45</t>
-        </is>
-      </c>
-      <c r="J102" s="70" t="inlineStr">
-        <is>
-          <t>El importe se muestra como '$2,280.45' (separador de miles y 2 decimales) en todas las pantallas</t>
-        </is>
-      </c>
-      <c r="K102" s="70" t="n"/>
-      <c r="L102" s="70" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="M102" s="70" t="inlineStr">
-        <is>
-          <t>[CASO NUEVO] Observado: se muestra '$2280.45' sin separador de miles</t>
-        </is>
-      </c>
-      <c r="N102" s="70" t="inlineStr">
-        <is>
-          <t>Por automatizar</t>
-        </is>
-      </c>
+      <c r="B102" s="73" t="n"/>
+      <c r="C102" s="73" t="n"/>
+      <c r="D102" s="74" t="n"/>
+      <c r="E102" s="75" t="n"/>
+      <c r="F102" s="73" t="n"/>
+      <c r="G102" s="73" t="n"/>
+      <c r="H102" s="73" t="n"/>
+      <c r="I102" s="73" t="n"/>
+      <c r="J102" s="73" t="n"/>
+      <c r="K102" s="73" t="n"/>
+      <c r="L102" s="73" t="n"/>
+      <c r="M102" s="73" t="n"/>
+      <c r="N102" s="73" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N102"/>
@@ -9675,7 +8100,7 @@
       </c>
       <c r="G6" s="79" t="inlineStr">
         <is>
-          <t>Happy path, validaciones de tarjeta, pagos aprobados (025, 029-031, 037-043, 050, 064, 090, 092)</t>
+          <t>Happy path, validaciones de tarjeta y pagos aprobados (025, 037-043, 050, 064, 090)</t>
         </is>
       </c>
     </row>
@@ -9739,7 +8164,7 @@
       </c>
       <c r="G8" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-026, 027, 028, 045</t>
+          <t>TC-BP-026, 027, 045</t>
         </is>
       </c>
     </row>
@@ -9867,7 +8292,7 @@
       </c>
       <c r="G12" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-095</t>
+          <t>- (sin casos activos)</t>
         </is>
       </c>
     </row>
@@ -9899,7 +8324,7 @@
       </c>
       <c r="G13" s="79" t="inlineStr">
         <is>
-          <t>Alterna de TC-BP-095</t>
+          <t>- (sin casos activos)</t>
         </is>
       </c>
     </row>
@@ -9931,7 +8356,7 @@
       </c>
       <c r="G14" s="79" t="inlineStr">
         <is>
-          <t>Rechazos y reintentos (032-035, 067-069, 094, 096)</t>
+          <t>Rechazos y reintentos (033, 035, 068, 094, 096)</t>
         </is>
       </c>
     </row>
@@ -9963,7 +8388,7 @@
       </c>
       <c r="G15" s="79" t="inlineStr">
         <is>
-          <t>Alterna de TC-BP-032 / 096</t>
+          <t>Alterna de TC-BP-096</t>
         </is>
       </c>
     </row>
@@ -10434,7 +8859,7 @@
       </c>
       <c r="I6" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-071</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -10518,7 +8943,7 @@
       </c>
       <c r="I8" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-010, 054, 055, 077</t>
+          <t>TC-BP-010, 054</t>
         </is>
       </c>
     </row>
@@ -10560,7 +8985,7 @@
       </c>
       <c r="I9" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-007, 009, 053, 078</t>
+          <t>TC-BP-007, 009, 053</t>
         </is>
       </c>
     </row>
@@ -10602,7 +9027,7 @@
       </c>
       <c r="I10" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-013, 057, 080</t>
+          <t>TC-BP-013</t>
         </is>
       </c>
     </row>
@@ -10644,7 +9069,7 @@
       </c>
       <c r="I11" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-014, 015, 079</t>
+          <t>TC-BP-014, 015</t>
         </is>
       </c>
     </row>
@@ -10686,7 +9111,7 @@
       </c>
       <c r="I12" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-057, 075, 080</t>
+          <t>TC-BP-012</t>
         </is>
       </c>
     </row>
@@ -10812,7 +9237,7 @@
       </c>
       <c r="I15" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-059, 060, 081</t>
+          <t>TC-BP-059, 060</t>
         </is>
       </c>
     </row>
@@ -10854,7 +9279,7 @@
       </c>
       <c r="I16" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-059, 081</t>
+          <t>TC-BP-059</t>
         </is>
       </c>
     </row>
@@ -10896,7 +9321,7 @@
       </c>
       <c r="I17" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-020, 061, 082</t>
+          <t>TC-BP-020, 061</t>
         </is>
       </c>
     </row>
@@ -10938,7 +9363,7 @@
       </c>
       <c r="I18" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-021, 062, 083</t>
+          <t>TC-BP-021, 062</t>
         </is>
       </c>
     </row>
@@ -11022,7 +9447,7 @@
       </c>
       <c r="I20" s="79" t="inlineStr">
         <is>
-          <t>TC-BP-084, 092</t>
+          <t>-</t>
         </is>
       </c>
     </row>
